--- a/panchang-data/Vicenza_Veneto2026.xlsx
+++ b/panchang-data/Vicenza_Veneto2026.xlsx
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9518" uniqueCount="5416">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9518" uniqueCount="5417">
   <si>
     <t>दिनाङ्क</t>
   </si>
@@ -16276,6 +16276,9 @@
   </si>
   <si>
     <t>121°04'20.91</t>
+  </si>
+  <si>
+    <t>ज्येष्ठ अधिक</t>
   </si>
 </sst>
 </file>
@@ -16765,7 +16768,7 @@
         <v>46023</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>28</v>
+        <v>89</v>
       </c>
       <c r="C2" s="2" t="s">
         <v>29</v>
@@ -16851,7 +16854,7 @@
         <v>46024</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>28</v>
+        <v>89</v>
       </c>
       <c r="C3" s="2" t="s">
         <v>50</v>
@@ -16937,7 +16940,7 @@
         <v>46025</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>28</v>
+        <v>89</v>
       </c>
       <c r="C4" s="2" t="s">
         <v>70</v>
@@ -17023,7 +17026,7 @@
         <v>46026</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>89</v>
+        <v>573</v>
       </c>
       <c r="C5" s="2" t="s">
         <v>90</v>
@@ -17109,7 +17112,7 @@
         <v>46027</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>89</v>
+        <v>573</v>
       </c>
       <c r="C6" s="2" t="s">
         <v>110</v>
@@ -17195,7 +17198,7 @@
         <v>46028</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>89</v>
+        <v>573</v>
       </c>
       <c r="C7" s="2" t="s">
         <v>127</v>
@@ -17281,7 +17284,7 @@
         <v>46029</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>89</v>
+        <v>573</v>
       </c>
       <c r="C8" s="2" t="s">
         <v>144</v>
@@ -17367,7 +17370,7 @@
         <v>46030</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>89</v>
+        <v>573</v>
       </c>
       <c r="C9" s="2" t="s">
         <v>29</v>
@@ -17453,7 +17456,7 @@
         <v>46031</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>89</v>
+        <v>573</v>
       </c>
       <c r="C10" s="2" t="s">
         <v>50</v>
@@ -17539,7 +17542,7 @@
         <v>46032</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>89</v>
+        <v>573</v>
       </c>
       <c r="C11" s="2" t="s">
         <v>70</v>
@@ -17625,7 +17628,7 @@
         <v>46033</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>89</v>
+        <v>573</v>
       </c>
       <c r="C12" s="2" t="s">
         <v>90</v>
@@ -17711,7 +17714,7 @@
         <v>46034</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>89</v>
+        <v>573</v>
       </c>
       <c r="C13" s="2" t="s">
         <v>110</v>
@@ -17797,7 +17800,7 @@
         <v>46035</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>89</v>
+        <v>573</v>
       </c>
       <c r="C14" s="2" t="s">
         <v>127</v>
@@ -17883,7 +17886,7 @@
         <v>46036</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>89</v>
+        <v>573</v>
       </c>
       <c r="C15" s="2" t="s">
         <v>144</v>
@@ -17969,7 +17972,7 @@
         <v>46037</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>89</v>
+        <v>573</v>
       </c>
       <c r="C16" s="2" t="s">
         <v>29</v>
@@ -18055,7 +18058,7 @@
         <v>46038</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>89</v>
+        <v>573</v>
       </c>
       <c r="C17" s="2" t="s">
         <v>50</v>
@@ -18141,7 +18144,7 @@
         <v>46039</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>89</v>
+        <v>573</v>
       </c>
       <c r="C18" s="2" t="s">
         <v>70</v>
@@ -18227,7 +18230,7 @@
         <v>46040</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>89</v>
+        <v>573</v>
       </c>
       <c r="C19" s="2" t="s">
         <v>90</v>
@@ -18313,7 +18316,7 @@
         <v>46041</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>89</v>
+        <v>573</v>
       </c>
       <c r="C20" s="2" t="s">
         <v>110</v>
@@ -18399,7 +18402,7 @@
         <v>46042</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>89</v>
+        <v>573</v>
       </c>
       <c r="C21" s="2" t="s">
         <v>127</v>
@@ -18485,7 +18488,7 @@
         <v>46043</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>89</v>
+        <v>573</v>
       </c>
       <c r="C22" s="2" t="s">
         <v>144</v>
@@ -18571,7 +18574,7 @@
         <v>46044</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>89</v>
+        <v>573</v>
       </c>
       <c r="C23" s="2" t="s">
         <v>29</v>
@@ -18657,7 +18660,7 @@
         <v>46045</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>89</v>
+        <v>573</v>
       </c>
       <c r="C24" s="2" t="s">
         <v>50</v>
@@ -18743,7 +18746,7 @@
         <v>46046</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>89</v>
+        <v>573</v>
       </c>
       <c r="C25" s="2" t="s">
         <v>70</v>
@@ -18829,7 +18832,7 @@
         <v>46047</v>
       </c>
       <c r="B26" s="2" t="s">
-        <v>89</v>
+        <v>573</v>
       </c>
       <c r="C26" s="2" t="s">
         <v>90</v>
@@ -18915,7 +18918,7 @@
         <v>46048</v>
       </c>
       <c r="B27" s="2" t="s">
-        <v>89</v>
+        <v>573</v>
       </c>
       <c r="C27" s="2" t="s">
         <v>110</v>
@@ -19001,7 +19004,7 @@
         <v>46049</v>
       </c>
       <c r="B28" s="2" t="s">
-        <v>89</v>
+        <v>573</v>
       </c>
       <c r="C28" s="2" t="s">
         <v>127</v>
@@ -19087,7 +19090,7 @@
         <v>46050</v>
       </c>
       <c r="B29" s="2" t="s">
-        <v>89</v>
+        <v>573</v>
       </c>
       <c r="C29" s="2" t="s">
         <v>144</v>
@@ -19173,7 +19176,7 @@
         <v>46051</v>
       </c>
       <c r="B30" s="2" t="s">
-        <v>89</v>
+        <v>573</v>
       </c>
       <c r="C30" s="2" t="s">
         <v>29</v>
@@ -19259,7 +19262,7 @@
         <v>46052</v>
       </c>
       <c r="B31" s="2" t="s">
-        <v>89</v>
+        <v>573</v>
       </c>
       <c r="C31" s="2" t="s">
         <v>50</v>
@@ -19345,7 +19348,7 @@
         <v>46053</v>
       </c>
       <c r="B32" s="2" t="s">
-        <v>89</v>
+        <v>573</v>
       </c>
       <c r="C32" s="2" t="s">
         <v>70</v>
@@ -19431,7 +19434,7 @@
         <v>46054</v>
       </c>
       <c r="B33" s="2" t="s">
-        <v>89</v>
+        <v>573</v>
       </c>
       <c r="C33" s="2" t="s">
         <v>90</v>
@@ -19517,7 +19520,7 @@
         <v>46055</v>
       </c>
       <c r="B34" s="2" t="s">
-        <v>573</v>
+        <v>1015</v>
       </c>
       <c r="C34" s="2" t="s">
         <v>110</v>
@@ -19603,7 +19606,7 @@
         <v>46056</v>
       </c>
       <c r="B35" s="2" t="s">
-        <v>573</v>
+        <v>1015</v>
       </c>
       <c r="C35" s="2" t="s">
         <v>127</v>
@@ -19689,7 +19692,7 @@
         <v>46057</v>
       </c>
       <c r="B36" s="2" t="s">
-        <v>573</v>
+        <v>1015</v>
       </c>
       <c r="C36" s="2" t="s">
         <v>144</v>
@@ -19775,7 +19778,7 @@
         <v>46058</v>
       </c>
       <c r="B37" s="2" t="s">
-        <v>573</v>
+        <v>1015</v>
       </c>
       <c r="C37" s="2" t="s">
         <v>29</v>
@@ -19861,7 +19864,7 @@
         <v>46059</v>
       </c>
       <c r="B38" s="2" t="s">
-        <v>573</v>
+        <v>1015</v>
       </c>
       <c r="C38" s="2" t="s">
         <v>50</v>
@@ -19947,7 +19950,7 @@
         <v>46060</v>
       </c>
       <c r="B39" s="2" t="s">
-        <v>573</v>
+        <v>1015</v>
       </c>
       <c r="C39" s="2" t="s">
         <v>70</v>
@@ -20033,7 +20036,7 @@
         <v>46061</v>
       </c>
       <c r="B40" s="2" t="s">
-        <v>573</v>
+        <v>1015</v>
       </c>
       <c r="C40" s="2" t="s">
         <v>90</v>
@@ -20119,7 +20122,7 @@
         <v>46062</v>
       </c>
       <c r="B41" s="2" t="s">
-        <v>573</v>
+        <v>1015</v>
       </c>
       <c r="C41" s="2" t="s">
         <v>110</v>
@@ -20205,7 +20208,7 @@
         <v>46063</v>
       </c>
       <c r="B42" s="2" t="s">
-        <v>573</v>
+        <v>1015</v>
       </c>
       <c r="C42" s="2" t="s">
         <v>127</v>
@@ -20291,7 +20294,7 @@
         <v>46064</v>
       </c>
       <c r="B43" s="2" t="s">
-        <v>573</v>
+        <v>1015</v>
       </c>
       <c r="C43" s="2" t="s">
         <v>144</v>
@@ -20377,7 +20380,7 @@
         <v>46065</v>
       </c>
       <c r="B44" s="2" t="s">
-        <v>573</v>
+        <v>1015</v>
       </c>
       <c r="C44" s="2" t="s">
         <v>29</v>
@@ -20463,7 +20466,7 @@
         <v>46066</v>
       </c>
       <c r="B45" s="2" t="s">
-        <v>573</v>
+        <v>1015</v>
       </c>
       <c r="C45" s="2" t="s">
         <v>50</v>
@@ -20549,7 +20552,7 @@
         <v>46067</v>
       </c>
       <c r="B46" s="2" t="s">
-        <v>573</v>
+        <v>1015</v>
       </c>
       <c r="C46" s="2" t="s">
         <v>70</v>
@@ -20635,7 +20638,7 @@
         <v>46068</v>
       </c>
       <c r="B47" s="2" t="s">
-        <v>573</v>
+        <v>1015</v>
       </c>
       <c r="C47" s="2" t="s">
         <v>90</v>
@@ -20721,7 +20724,7 @@
         <v>46069</v>
       </c>
       <c r="B48" s="2" t="s">
-        <v>573</v>
+        <v>1015</v>
       </c>
       <c r="C48" s="2" t="s">
         <v>110</v>
@@ -20807,7 +20810,7 @@
         <v>46070</v>
       </c>
       <c r="B49" s="2" t="s">
-        <v>573</v>
+        <v>1015</v>
       </c>
       <c r="C49" s="2" t="s">
         <v>127</v>
@@ -20893,7 +20896,7 @@
         <v>46071</v>
       </c>
       <c r="B50" s="2" t="s">
-        <v>573</v>
+        <v>1015</v>
       </c>
       <c r="C50" s="2" t="s">
         <v>144</v>
@@ -20979,7 +20982,7 @@
         <v>46072</v>
       </c>
       <c r="B51" s="2" t="s">
-        <v>573</v>
+        <v>1015</v>
       </c>
       <c r="C51" s="2" t="s">
         <v>29</v>
@@ -21065,7 +21068,7 @@
         <v>46073</v>
       </c>
       <c r="B52" s="2" t="s">
-        <v>573</v>
+        <v>1015</v>
       </c>
       <c r="C52" s="2" t="s">
         <v>50</v>
@@ -21151,7 +21154,7 @@
         <v>46074</v>
       </c>
       <c r="B53" s="2" t="s">
-        <v>573</v>
+        <v>1015</v>
       </c>
       <c r="C53" s="2" t="s">
         <v>70</v>
@@ -21237,7 +21240,7 @@
         <v>46075</v>
       </c>
       <c r="B54" s="2" t="s">
-        <v>573</v>
+        <v>1015</v>
       </c>
       <c r="C54" s="2" t="s">
         <v>90</v>
@@ -21323,7 +21326,7 @@
         <v>46076</v>
       </c>
       <c r="B55" s="2" t="s">
-        <v>573</v>
+        <v>1015</v>
       </c>
       <c r="C55" s="2" t="s">
         <v>110</v>
@@ -21409,7 +21412,7 @@
         <v>46077</v>
       </c>
       <c r="B56" s="2" t="s">
-        <v>573</v>
+        <v>1015</v>
       </c>
       <c r="C56" s="2" t="s">
         <v>127</v>
@@ -21495,7 +21498,7 @@
         <v>46078</v>
       </c>
       <c r="B57" s="2" t="s">
-        <v>573</v>
+        <v>1015</v>
       </c>
       <c r="C57" s="2" t="s">
         <v>144</v>
@@ -21581,7 +21584,7 @@
         <v>46079</v>
       </c>
       <c r="B58" s="2" t="s">
-        <v>573</v>
+        <v>1015</v>
       </c>
       <c r="C58" s="2" t="s">
         <v>29</v>
@@ -21667,7 +21670,7 @@
         <v>46080</v>
       </c>
       <c r="B59" s="2" t="s">
-        <v>573</v>
+        <v>1015</v>
       </c>
       <c r="C59" s="2" t="s">
         <v>50</v>
@@ -21753,7 +21756,7 @@
         <v>46081</v>
       </c>
       <c r="B60" s="2" t="s">
-        <v>573</v>
+        <v>1015</v>
       </c>
       <c r="C60" s="2" t="s">
         <v>70</v>
@@ -21839,7 +21842,7 @@
         <v>46082</v>
       </c>
       <c r="B61" s="2" t="s">
-        <v>573</v>
+        <v>1015</v>
       </c>
       <c r="C61" s="2" t="s">
         <v>90</v>
@@ -21925,7 +21928,7 @@
         <v>46083</v>
       </c>
       <c r="B62" s="2" t="s">
-        <v>573</v>
+        <v>1015</v>
       </c>
       <c r="C62" s="2" t="s">
         <v>110</v>
@@ -22011,7 +22014,7 @@
         <v>46084</v>
       </c>
       <c r="B63" s="2" t="s">
-        <v>573</v>
+        <v>1015</v>
       </c>
       <c r="C63" s="2" t="s">
         <v>127</v>
@@ -22097,7 +22100,7 @@
         <v>46085</v>
       </c>
       <c r="B64" s="2" t="s">
-        <v>1015</v>
+        <v>1438</v>
       </c>
       <c r="C64" s="2" t="s">
         <v>144</v>
@@ -22183,7 +22186,7 @@
         <v>46086</v>
       </c>
       <c r="B65" s="2" t="s">
-        <v>1015</v>
+        <v>1438</v>
       </c>
       <c r="C65" s="2" t="s">
         <v>29</v>
@@ -22269,7 +22272,7 @@
         <v>46087</v>
       </c>
       <c r="B66" s="2" t="s">
-        <v>1015</v>
+        <v>1438</v>
       </c>
       <c r="C66" s="2" t="s">
         <v>50</v>
@@ -22355,7 +22358,7 @@
         <v>46088</v>
       </c>
       <c r="B67" s="2" t="s">
-        <v>1015</v>
+        <v>1438</v>
       </c>
       <c r="C67" s="2" t="s">
         <v>70</v>
@@ -22441,7 +22444,7 @@
         <v>46089</v>
       </c>
       <c r="B68" s="2" t="s">
-        <v>1015</v>
+        <v>1438</v>
       </c>
       <c r="C68" s="2" t="s">
         <v>90</v>
@@ -22527,7 +22530,7 @@
         <v>46090</v>
       </c>
       <c r="B69" s="2" t="s">
-        <v>1015</v>
+        <v>1438</v>
       </c>
       <c r="C69" s="2" t="s">
         <v>110</v>
@@ -22613,7 +22616,7 @@
         <v>46091</v>
       </c>
       <c r="B70" s="2" t="s">
-        <v>1015</v>
+        <v>1438</v>
       </c>
       <c r="C70" s="2" t="s">
         <v>127</v>
@@ -22699,7 +22702,7 @@
         <v>46092</v>
       </c>
       <c r="B71" s="2" t="s">
-        <v>1015</v>
+        <v>1438</v>
       </c>
       <c r="C71" s="2" t="s">
         <v>144</v>
@@ -22785,7 +22788,7 @@
         <v>46093</v>
       </c>
       <c r="B72" s="2" t="s">
-        <v>1015</v>
+        <v>1438</v>
       </c>
       <c r="C72" s="2" t="s">
         <v>29</v>
@@ -22871,7 +22874,7 @@
         <v>46094</v>
       </c>
       <c r="B73" s="2" t="s">
-        <v>1015</v>
+        <v>1438</v>
       </c>
       <c r="C73" s="2" t="s">
         <v>50</v>
@@ -22957,7 +22960,7 @@
         <v>46095</v>
       </c>
       <c r="B74" s="2" t="s">
-        <v>1015</v>
+        <v>1438</v>
       </c>
       <c r="C74" s="2" t="s">
         <v>70</v>
@@ -23043,7 +23046,7 @@
         <v>46096</v>
       </c>
       <c r="B75" s="2" t="s">
-        <v>1015</v>
+        <v>1438</v>
       </c>
       <c r="C75" s="2" t="s">
         <v>90</v>
@@ -23129,7 +23132,7 @@
         <v>46097</v>
       </c>
       <c r="B76" s="2" t="s">
-        <v>1015</v>
+        <v>1438</v>
       </c>
       <c r="C76" s="2" t="s">
         <v>110</v>
@@ -23215,7 +23218,7 @@
         <v>46098</v>
       </c>
       <c r="B77" s="2" t="s">
-        <v>1015</v>
+        <v>1438</v>
       </c>
       <c r="C77" s="2" t="s">
         <v>127</v>
@@ -23301,7 +23304,7 @@
         <v>46099</v>
       </c>
       <c r="B78" s="2" t="s">
-        <v>1015</v>
+        <v>1438</v>
       </c>
       <c r="C78" s="2" t="s">
         <v>144</v>
@@ -23387,7 +23390,7 @@
         <v>46100</v>
       </c>
       <c r="B79" s="2" t="s">
-        <v>1015</v>
+        <v>1438</v>
       </c>
       <c r="C79" s="2" t="s">
         <v>29</v>
@@ -23473,7 +23476,7 @@
         <v>46101</v>
       </c>
       <c r="B80" s="2" t="s">
-        <v>1015</v>
+        <v>1438</v>
       </c>
       <c r="C80" s="2" t="s">
         <v>50</v>
@@ -23559,7 +23562,7 @@
         <v>46102</v>
       </c>
       <c r="B81" s="2" t="s">
-        <v>1015</v>
+        <v>1438</v>
       </c>
       <c r="C81" s="2" t="s">
         <v>70</v>
@@ -23645,7 +23648,7 @@
         <v>46103</v>
       </c>
       <c r="B82" s="2" t="s">
-        <v>1015</v>
+        <v>1438</v>
       </c>
       <c r="C82" s="2" t="s">
         <v>90</v>
@@ -23731,7 +23734,7 @@
         <v>46104</v>
       </c>
       <c r="B83" s="2" t="s">
-        <v>1015</v>
+        <v>1438</v>
       </c>
       <c r="C83" s="2" t="s">
         <v>110</v>
@@ -23817,7 +23820,7 @@
         <v>46105</v>
       </c>
       <c r="B84" s="2" t="s">
-        <v>1015</v>
+        <v>1438</v>
       </c>
       <c r="C84" s="2" t="s">
         <v>127</v>
@@ -23903,7 +23906,7 @@
         <v>46106</v>
       </c>
       <c r="B85" s="2" t="s">
-        <v>1015</v>
+        <v>1438</v>
       </c>
       <c r="C85" s="2" t="s">
         <v>144</v>
@@ -23989,7 +23992,7 @@
         <v>46107</v>
       </c>
       <c r="B86" s="2" t="s">
-        <v>1015</v>
+        <v>1438</v>
       </c>
       <c r="C86" s="2" t="s">
         <v>29</v>
@@ -24075,7 +24078,7 @@
         <v>46108</v>
       </c>
       <c r="B87" s="2" t="s">
-        <v>1015</v>
+        <v>1438</v>
       </c>
       <c r="C87" s="2" t="s">
         <v>50</v>
@@ -24161,7 +24164,7 @@
         <v>46109</v>
       </c>
       <c r="B88" s="2" t="s">
-        <v>1015</v>
+        <v>1438</v>
       </c>
       <c r="C88" s="2" t="s">
         <v>70</v>
@@ -24247,7 +24250,7 @@
         <v>46110</v>
       </c>
       <c r="B89" s="2" t="s">
-        <v>1015</v>
+        <v>1438</v>
       </c>
       <c r="C89" s="2" t="s">
         <v>90</v>
@@ -24333,7 +24336,7 @@
         <v>46111</v>
       </c>
       <c r="B90" s="2" t="s">
-        <v>1015</v>
+        <v>1438</v>
       </c>
       <c r="C90" s="2" t="s">
         <v>110</v>
@@ -24419,7 +24422,7 @@
         <v>46112</v>
       </c>
       <c r="B91" s="2" t="s">
-        <v>1015</v>
+        <v>1438</v>
       </c>
       <c r="C91" s="2" t="s">
         <v>127</v>
@@ -24505,7 +24508,7 @@
         <v>46113</v>
       </c>
       <c r="B92" s="2" t="s">
-        <v>1015</v>
+        <v>1438</v>
       </c>
       <c r="C92" s="2" t="s">
         <v>144</v>
@@ -24591,7 +24594,7 @@
         <v>46114</v>
       </c>
       <c r="B93" s="2" t="s">
-        <v>1438</v>
+        <v>1877</v>
       </c>
       <c r="C93" s="2" t="s">
         <v>29</v>
@@ -24677,7 +24680,7 @@
         <v>46115</v>
       </c>
       <c r="B94" s="2" t="s">
-        <v>1438</v>
+        <v>1877</v>
       </c>
       <c r="C94" s="2" t="s">
         <v>50</v>
@@ -24763,7 +24766,7 @@
         <v>46116</v>
       </c>
       <c r="B95" s="2" t="s">
-        <v>1438</v>
+        <v>1877</v>
       </c>
       <c r="C95" s="2" t="s">
         <v>70</v>
@@ -24849,7 +24852,7 @@
         <v>46117</v>
       </c>
       <c r="B96" s="2" t="s">
-        <v>1438</v>
+        <v>1877</v>
       </c>
       <c r="C96" s="2" t="s">
         <v>90</v>
@@ -24935,7 +24938,7 @@
         <v>46118</v>
       </c>
       <c r="B97" s="2" t="s">
-        <v>1438</v>
+        <v>1877</v>
       </c>
       <c r="C97" s="2" t="s">
         <v>110</v>
@@ -25021,7 +25024,7 @@
         <v>46119</v>
       </c>
       <c r="B98" s="2" t="s">
-        <v>1438</v>
+        <v>1877</v>
       </c>
       <c r="C98" s="2" t="s">
         <v>127</v>
@@ -25107,7 +25110,7 @@
         <v>46120</v>
       </c>
       <c r="B99" s="2" t="s">
-        <v>1438</v>
+        <v>1877</v>
       </c>
       <c r="C99" s="2" t="s">
         <v>144</v>
@@ -25193,7 +25196,7 @@
         <v>46121</v>
       </c>
       <c r="B100" s="2" t="s">
-        <v>1438</v>
+        <v>1877</v>
       </c>
       <c r="C100" s="2" t="s">
         <v>29</v>
@@ -25279,7 +25282,7 @@
         <v>46122</v>
       </c>
       <c r="B101" s="2" t="s">
-        <v>1438</v>
+        <v>1877</v>
       </c>
       <c r="C101" s="2" t="s">
         <v>50</v>
@@ -25365,7 +25368,7 @@
         <v>46123</v>
       </c>
       <c r="B102" s="2" t="s">
-        <v>1438</v>
+        <v>1877</v>
       </c>
       <c r="C102" s="2" t="s">
         <v>70</v>
@@ -25451,7 +25454,7 @@
         <v>46124</v>
       </c>
       <c r="B103" s="2" t="s">
-        <v>1438</v>
+        <v>1877</v>
       </c>
       <c r="C103" s="2" t="s">
         <v>90</v>
@@ -25537,7 +25540,7 @@
         <v>46125</v>
       </c>
       <c r="B104" s="2" t="s">
-        <v>1438</v>
+        <v>1877</v>
       </c>
       <c r="C104" s="2" t="s">
         <v>110</v>
@@ -25623,7 +25626,7 @@
         <v>46126</v>
       </c>
       <c r="B105" s="2" t="s">
-        <v>1438</v>
+        <v>1877</v>
       </c>
       <c r="C105" s="2" t="s">
         <v>127</v>
@@ -25709,7 +25712,7 @@
         <v>46127</v>
       </c>
       <c r="B106" s="2" t="s">
-        <v>1438</v>
+        <v>1877</v>
       </c>
       <c r="C106" s="2" t="s">
         <v>144</v>
@@ -25795,7 +25798,7 @@
         <v>46128</v>
       </c>
       <c r="B107" s="2" t="s">
-        <v>1438</v>
+        <v>1877</v>
       </c>
       <c r="C107" s="2" t="s">
         <v>29</v>
@@ -25881,7 +25884,7 @@
         <v>46129</v>
       </c>
       <c r="B108" s="2" t="s">
-        <v>1438</v>
+        <v>1877</v>
       </c>
       <c r="C108" s="2" t="s">
         <v>50</v>
@@ -25967,7 +25970,7 @@
         <v>46130</v>
       </c>
       <c r="B109" s="2" t="s">
-        <v>1438</v>
+        <v>1877</v>
       </c>
       <c r="C109" s="2" t="s">
         <v>70</v>
@@ -26053,7 +26056,7 @@
         <v>46131</v>
       </c>
       <c r="B110" s="2" t="s">
-        <v>1438</v>
+        <v>1877</v>
       </c>
       <c r="C110" s="2" t="s">
         <v>90</v>
@@ -26139,7 +26142,7 @@
         <v>46132</v>
       </c>
       <c r="B111" s="2" t="s">
-        <v>1438</v>
+        <v>1877</v>
       </c>
       <c r="C111" s="2" t="s">
         <v>110</v>
@@ -26225,7 +26228,7 @@
         <v>46133</v>
       </c>
       <c r="B112" s="2" t="s">
-        <v>1438</v>
+        <v>1877</v>
       </c>
       <c r="C112" s="2" t="s">
         <v>127</v>
@@ -26311,7 +26314,7 @@
         <v>46134</v>
       </c>
       <c r="B113" s="2" t="s">
-        <v>1438</v>
+        <v>1877</v>
       </c>
       <c r="C113" s="2" t="s">
         <v>144</v>
@@ -26397,7 +26400,7 @@
         <v>46135</v>
       </c>
       <c r="B114" s="2" t="s">
-        <v>1438</v>
+        <v>1877</v>
       </c>
       <c r="C114" s="2" t="s">
         <v>29</v>
@@ -26483,7 +26486,7 @@
         <v>46136</v>
       </c>
       <c r="B115" s="2" t="s">
-        <v>1438</v>
+        <v>1877</v>
       </c>
       <c r="C115" s="2" t="s">
         <v>50</v>
@@ -26569,7 +26572,7 @@
         <v>46137</v>
       </c>
       <c r="B116" s="2" t="s">
-        <v>1438</v>
+        <v>1877</v>
       </c>
       <c r="C116" s="2" t="s">
         <v>70</v>
@@ -26655,7 +26658,7 @@
         <v>46138</v>
       </c>
       <c r="B117" s="2" t="s">
-        <v>1438</v>
+        <v>1877</v>
       </c>
       <c r="C117" s="2" t="s">
         <v>90</v>
@@ -26741,7 +26744,7 @@
         <v>46139</v>
       </c>
       <c r="B118" s="2" t="s">
-        <v>1438</v>
+        <v>1877</v>
       </c>
       <c r="C118" s="2" t="s">
         <v>110</v>
@@ -26827,7 +26830,7 @@
         <v>46140</v>
       </c>
       <c r="B119" s="2" t="s">
-        <v>1438</v>
+        <v>1877</v>
       </c>
       <c r="C119" s="2" t="s">
         <v>127</v>
@@ -26913,7 +26916,7 @@
         <v>46141</v>
       </c>
       <c r="B120" s="2" t="s">
-        <v>1438</v>
+        <v>1877</v>
       </c>
       <c r="C120" s="2" t="s">
         <v>144</v>
@@ -26999,7 +27002,7 @@
         <v>46142</v>
       </c>
       <c r="B121" s="2" t="s">
-        <v>1438</v>
+        <v>1877</v>
       </c>
       <c r="C121" s="2" t="s">
         <v>29</v>
@@ -27085,7 +27088,7 @@
         <v>46143</v>
       </c>
       <c r="B122" s="2" t="s">
-        <v>1438</v>
+        <v>1877</v>
       </c>
       <c r="C122" s="2" t="s">
         <v>50</v>
@@ -27171,7 +27174,7 @@
         <v>46144</v>
       </c>
       <c r="B123" s="2" t="s">
-        <v>1877</v>
+        <v>2316</v>
       </c>
       <c r="C123" s="2" t="s">
         <v>70</v>
@@ -27257,7 +27260,7 @@
         <v>46145</v>
       </c>
       <c r="B124" s="2" t="s">
-        <v>1877</v>
+        <v>2316</v>
       </c>
       <c r="C124" s="2" t="s">
         <v>90</v>
@@ -27343,7 +27346,7 @@
         <v>46146</v>
       </c>
       <c r="B125" s="2" t="s">
-        <v>1877</v>
+        <v>2316</v>
       </c>
       <c r="C125" s="2" t="s">
         <v>110</v>
@@ -27429,7 +27432,7 @@
         <v>46147</v>
       </c>
       <c r="B126" s="2" t="s">
-        <v>1877</v>
+        <v>2316</v>
       </c>
       <c r="C126" s="2" t="s">
         <v>127</v>
@@ -27515,7 +27518,7 @@
         <v>46148</v>
       </c>
       <c r="B127" s="2" t="s">
-        <v>1877</v>
+        <v>2316</v>
       </c>
       <c r="C127" s="2" t="s">
         <v>144</v>
@@ -27601,7 +27604,7 @@
         <v>46149</v>
       </c>
       <c r="B128" s="2" t="s">
-        <v>1877</v>
+        <v>2316</v>
       </c>
       <c r="C128" s="2" t="s">
         <v>29</v>
@@ -27687,7 +27690,7 @@
         <v>46150</v>
       </c>
       <c r="B129" s="2" t="s">
-        <v>1877</v>
+        <v>2316</v>
       </c>
       <c r="C129" s="2" t="s">
         <v>50</v>
@@ -27773,7 +27776,7 @@
         <v>46151</v>
       </c>
       <c r="B130" s="2" t="s">
-        <v>1877</v>
+        <v>2316</v>
       </c>
       <c r="C130" s="2" t="s">
         <v>70</v>
@@ -27859,7 +27862,7 @@
         <v>46152</v>
       </c>
       <c r="B131" s="2" t="s">
-        <v>1877</v>
+        <v>2316</v>
       </c>
       <c r="C131" s="2" t="s">
         <v>90</v>
@@ -27945,7 +27948,7 @@
         <v>46153</v>
       </c>
       <c r="B132" s="2" t="s">
-        <v>1877</v>
+        <v>2316</v>
       </c>
       <c r="C132" s="2" t="s">
         <v>110</v>
@@ -28031,7 +28034,7 @@
         <v>46154</v>
       </c>
       <c r="B133" s="2" t="s">
-        <v>1877</v>
+        <v>2316</v>
       </c>
       <c r="C133" s="2" t="s">
         <v>127</v>
@@ -28117,7 +28120,7 @@
         <v>46155</v>
       </c>
       <c r="B134" s="2" t="s">
-        <v>1877</v>
+        <v>2316</v>
       </c>
       <c r="C134" s="2" t="s">
         <v>144</v>
@@ -28203,7 +28206,7 @@
         <v>46156</v>
       </c>
       <c r="B135" s="2" t="s">
-        <v>1877</v>
+        <v>2316</v>
       </c>
       <c r="C135" s="2" t="s">
         <v>29</v>
@@ -28289,7 +28292,7 @@
         <v>46157</v>
       </c>
       <c r="B136" s="2" t="s">
-        <v>1877</v>
+        <v>2316</v>
       </c>
       <c r="C136" s="2" t="s">
         <v>50</v>
@@ -28375,7 +28378,7 @@
         <v>46158</v>
       </c>
       <c r="B137" s="2" t="s">
-        <v>1877</v>
+        <v>2316</v>
       </c>
       <c r="C137" s="2" t="s">
         <v>70</v>
@@ -28461,7 +28464,7 @@
         <v>46159</v>
       </c>
       <c r="B138" s="2" t="s">
-        <v>1877</v>
+        <v>5416</v>
       </c>
       <c r="C138" s="2" t="s">
         <v>90</v>
@@ -28547,7 +28550,7 @@
         <v>46160</v>
       </c>
       <c r="B139" s="2" t="s">
-        <v>1877</v>
+        <v>5416</v>
       </c>
       <c r="C139" s="2" t="s">
         <v>110</v>
@@ -28633,7 +28636,7 @@
         <v>46161</v>
       </c>
       <c r="B140" s="2" t="s">
-        <v>1877</v>
+        <v>5416</v>
       </c>
       <c r="C140" s="2" t="s">
         <v>127</v>
@@ -28719,7 +28722,7 @@
         <v>46162</v>
       </c>
       <c r="B141" s="2" t="s">
-        <v>1877</v>
+        <v>5416</v>
       </c>
       <c r="C141" s="2" t="s">
         <v>144</v>
@@ -28805,7 +28808,7 @@
         <v>46163</v>
       </c>
       <c r="B142" s="2" t="s">
-        <v>1877</v>
+        <v>5416</v>
       </c>
       <c r="C142" s="2" t="s">
         <v>29</v>
@@ -28891,7 +28894,7 @@
         <v>46164</v>
       </c>
       <c r="B143" s="2" t="s">
-        <v>1877</v>
+        <v>5416</v>
       </c>
       <c r="C143" s="2" t="s">
         <v>50</v>
@@ -28977,7 +28980,7 @@
         <v>46165</v>
       </c>
       <c r="B144" s="2" t="s">
-        <v>1877</v>
+        <v>5416</v>
       </c>
       <c r="C144" s="2" t="s">
         <v>70</v>
@@ -29063,7 +29066,7 @@
         <v>46166</v>
       </c>
       <c r="B145" s="2" t="s">
-        <v>1877</v>
+        <v>5416</v>
       </c>
       <c r="C145" s="2" t="s">
         <v>90</v>
@@ -29149,7 +29152,7 @@
         <v>46167</v>
       </c>
       <c r="B146" s="2" t="s">
-        <v>1877</v>
+        <v>5416</v>
       </c>
       <c r="C146" s="2" t="s">
         <v>110</v>
@@ -29235,7 +29238,7 @@
         <v>46168</v>
       </c>
       <c r="B147" s="2" t="s">
-        <v>1877</v>
+        <v>5416</v>
       </c>
       <c r="C147" s="2" t="s">
         <v>127</v>
@@ -29321,7 +29324,7 @@
         <v>46169</v>
       </c>
       <c r="B148" s="2" t="s">
-        <v>1877</v>
+        <v>5416</v>
       </c>
       <c r="C148" s="2" t="s">
         <v>144</v>
@@ -29407,7 +29410,7 @@
         <v>46170</v>
       </c>
       <c r="B149" s="2" t="s">
-        <v>1877</v>
+        <v>5416</v>
       </c>
       <c r="C149" s="2" t="s">
         <v>29</v>
@@ -29493,7 +29496,7 @@
         <v>46171</v>
       </c>
       <c r="B150" s="2" t="s">
-        <v>1877</v>
+        <v>5416</v>
       </c>
       <c r="C150" s="2" t="s">
         <v>50</v>
@@ -29579,7 +29582,7 @@
         <v>46172</v>
       </c>
       <c r="B151" s="2" t="s">
-        <v>1877</v>
+        <v>5416</v>
       </c>
       <c r="C151" s="2" t="s">
         <v>70</v>
@@ -29665,7 +29668,7 @@
         <v>46173</v>
       </c>
       <c r="B152" s="2" t="s">
-        <v>1877</v>
+        <v>5416</v>
       </c>
       <c r="C152" s="2" t="s">
         <v>90</v>
@@ -29751,7 +29754,7 @@
         <v>46174</v>
       </c>
       <c r="B153" s="2" t="s">
-        <v>2316</v>
+        <v>5416</v>
       </c>
       <c r="C153" s="2" t="s">
         <v>110</v>
@@ -29837,7 +29840,7 @@
         <v>46175</v>
       </c>
       <c r="B154" s="2" t="s">
-        <v>2316</v>
+        <v>5416</v>
       </c>
       <c r="C154" s="2" t="s">
         <v>127</v>
@@ -29923,7 +29926,7 @@
         <v>46176</v>
       </c>
       <c r="B155" s="2" t="s">
-        <v>2316</v>
+        <v>5416</v>
       </c>
       <c r="C155" s="2" t="s">
         <v>144</v>
@@ -30009,7 +30012,7 @@
         <v>46177</v>
       </c>
       <c r="B156" s="2" t="s">
-        <v>2316</v>
+        <v>5416</v>
       </c>
       <c r="C156" s="2" t="s">
         <v>29</v>
@@ -30095,7 +30098,7 @@
         <v>46178</v>
       </c>
       <c r="B157" s="2" t="s">
-        <v>2316</v>
+        <v>5416</v>
       </c>
       <c r="C157" s="2" t="s">
         <v>50</v>
@@ -30181,7 +30184,7 @@
         <v>46179</v>
       </c>
       <c r="B158" s="2" t="s">
-        <v>2316</v>
+        <v>5416</v>
       </c>
       <c r="C158" s="2" t="s">
         <v>70</v>
@@ -30267,7 +30270,7 @@
         <v>46180</v>
       </c>
       <c r="B159" s="2" t="s">
-        <v>2316</v>
+        <v>5416</v>
       </c>
       <c r="C159" s="2" t="s">
         <v>90</v>
@@ -30353,7 +30356,7 @@
         <v>46181</v>
       </c>
       <c r="B160" s="2" t="s">
-        <v>2316</v>
+        <v>5416</v>
       </c>
       <c r="C160" s="2" t="s">
         <v>110</v>
@@ -30439,7 +30442,7 @@
         <v>46182</v>
       </c>
       <c r="B161" s="2" t="s">
-        <v>2316</v>
+        <v>5416</v>
       </c>
       <c r="C161" s="2" t="s">
         <v>127</v>
@@ -30525,7 +30528,7 @@
         <v>46183</v>
       </c>
       <c r="B162" s="2" t="s">
-        <v>2316</v>
+        <v>5416</v>
       </c>
       <c r="C162" s="2" t="s">
         <v>144</v>
@@ -30611,7 +30614,7 @@
         <v>46184</v>
       </c>
       <c r="B163" s="2" t="s">
-        <v>2316</v>
+        <v>5416</v>
       </c>
       <c r="C163" s="2" t="s">
         <v>29</v>
@@ -30697,7 +30700,7 @@
         <v>46185</v>
       </c>
       <c r="B164" s="2" t="s">
-        <v>2316</v>
+        <v>5416</v>
       </c>
       <c r="C164" s="2" t="s">
         <v>50</v>
@@ -30783,7 +30786,7 @@
         <v>46186</v>
       </c>
       <c r="B165" s="2" t="s">
-        <v>2316</v>
+        <v>5416</v>
       </c>
       <c r="C165" s="2" t="s">
         <v>70</v>
@@ -30869,7 +30872,7 @@
         <v>46187</v>
       </c>
       <c r="B166" s="2" t="s">
-        <v>2316</v>
+        <v>5416</v>
       </c>
       <c r="C166" s="2" t="s">
         <v>90</v>
